--- a/artfynd/A 11125-2026 artfynd.xlsx
+++ b/artfynd/A 11125-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136703532</v>
       </c>
       <c r="B2" t="n">
-        <v>79506</v>
+        <v>79508</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136703530</v>
       </c>
       <c r="B3" t="n">
-        <v>79569</v>
+        <v>79571</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136703536</v>
       </c>
       <c r="B4" t="n">
-        <v>92285</v>
+        <v>92290</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136703519</v>
       </c>
       <c r="B5" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136703531</v>
       </c>
       <c r="B6" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136703534</v>
       </c>
       <c r="B7" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136703538</v>
       </c>
       <c r="B8" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136703522</v>
       </c>
       <c r="B9" t="n">
-        <v>79231</v>
+        <v>79233</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>136703525</v>
       </c>
       <c r="B10" t="n">
-        <v>79231</v>
+        <v>79233</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>136703533</v>
       </c>
       <c r="B11" t="n">
-        <v>79231</v>
+        <v>79233</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>136703535</v>
       </c>
       <c r="B12" t="n">
-        <v>79231</v>
+        <v>79233</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>136703521</v>
       </c>
       <c r="B13" t="n">
-        <v>80093</v>
+        <v>80095</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>136703523</v>
       </c>
       <c r="B14" t="n">
-        <v>80093</v>
+        <v>80095</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>136703524</v>
       </c>
       <c r="B15" t="n">
-        <v>80093</v>
+        <v>80095</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>136703526</v>
       </c>
       <c r="B16" t="n">
-        <v>80093</v>
+        <v>80095</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         <v>136703528</v>
       </c>
       <c r="B17" t="n">
-        <v>80093</v>
+        <v>80095</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         <v>136703537</v>
       </c>
       <c r="B18" t="n">
-        <v>80093</v>
+        <v>80095</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>136703518</v>
       </c>
       <c r="B19" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2519,7 +2519,7 @@
         <v>136703527</v>
       </c>
       <c r="B20" t="n">
-        <v>80064</v>
+        <v>80066</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2621,7 +2621,7 @@
         <v>136703529</v>
       </c>
       <c r="B21" t="n">
-        <v>80064</v>
+        <v>80066</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 11125-2026 artfynd.xlsx
+++ b/artfynd/A 11125-2026 artfynd.xlsx
@@ -887,7 +887,7 @@
         <v>136703536</v>
       </c>
       <c r="B4" t="n">
-        <v>92290</v>
+        <v>92292</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 11125-2026 artfynd.xlsx
+++ b/artfynd/A 11125-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136703532</v>
       </c>
       <c r="B2" t="n">
-        <v>79508</v>
+        <v>79512</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136703530</v>
       </c>
       <c r="B3" t="n">
-        <v>79571</v>
+        <v>79575</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136703536</v>
       </c>
       <c r="B4" t="n">
-        <v>92292</v>
+        <v>92294</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136703519</v>
       </c>
       <c r="B5" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136703531</v>
       </c>
       <c r="B6" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136703534</v>
       </c>
       <c r="B7" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136703538</v>
       </c>
       <c r="B8" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136703522</v>
       </c>
       <c r="B9" t="n">
-        <v>79233</v>
+        <v>79237</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>136703525</v>
       </c>
       <c r="B10" t="n">
-        <v>79233</v>
+        <v>79237</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>136703533</v>
       </c>
       <c r="B11" t="n">
-        <v>79233</v>
+        <v>79237</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>136703535</v>
       </c>
       <c r="B12" t="n">
-        <v>79233</v>
+        <v>79237</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>136703521</v>
       </c>
       <c r="B13" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>136703523</v>
       </c>
       <c r="B14" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>136703524</v>
       </c>
       <c r="B15" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>136703526</v>
       </c>
       <c r="B16" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         <v>136703528</v>
       </c>
       <c r="B17" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         <v>136703537</v>
       </c>
       <c r="B18" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2519,7 +2519,7 @@
         <v>136703527</v>
       </c>
       <c r="B20" t="n">
-        <v>80066</v>
+        <v>80070</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2621,7 +2621,7 @@
         <v>136703529</v>
       </c>
       <c r="B21" t="n">
-        <v>80066</v>
+        <v>80070</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 11125-2026 artfynd.xlsx
+++ b/artfynd/A 11125-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136703532</v>
       </c>
       <c r="B2" t="n">
-        <v>79512</v>
+        <v>79514</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136703530</v>
       </c>
       <c r="B3" t="n">
-        <v>79575</v>
+        <v>79577</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136703536</v>
       </c>
       <c r="B4" t="n">
-        <v>92294</v>
+        <v>92296</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136703519</v>
       </c>
       <c r="B5" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136703531</v>
       </c>
       <c r="B6" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136703534</v>
       </c>
       <c r="B7" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136703538</v>
       </c>
       <c r="B8" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136703522</v>
       </c>
       <c r="B9" t="n">
-        <v>79237</v>
+        <v>79239</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>136703525</v>
       </c>
       <c r="B10" t="n">
-        <v>79237</v>
+        <v>79239</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>136703533</v>
       </c>
       <c r="B11" t="n">
-        <v>79237</v>
+        <v>79239</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>136703535</v>
       </c>
       <c r="B12" t="n">
-        <v>79237</v>
+        <v>79239</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>136703521</v>
       </c>
       <c r="B13" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>136703523</v>
       </c>
       <c r="B14" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>136703524</v>
       </c>
       <c r="B15" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>136703526</v>
       </c>
       <c r="B16" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         <v>136703528</v>
       </c>
       <c r="B17" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         <v>136703537</v>
       </c>
       <c r="B18" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2519,7 +2519,7 @@
         <v>136703527</v>
       </c>
       <c r="B20" t="n">
-        <v>80070</v>
+        <v>80072</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2621,7 +2621,7 @@
         <v>136703529</v>
       </c>
       <c r="B21" t="n">
-        <v>80070</v>
+        <v>80072</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 11125-2026 artfynd.xlsx
+++ b/artfynd/A 11125-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136703532</v>
       </c>
       <c r="B2" t="n">
-        <v>79514</v>
+        <v>79515</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136703530</v>
       </c>
       <c r="B3" t="n">
-        <v>79577</v>
+        <v>79578</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136703536</v>
       </c>
       <c r="B4" t="n">
-        <v>92296</v>
+        <v>92297</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136703519</v>
       </c>
       <c r="B5" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136703531</v>
       </c>
       <c r="B6" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136703534</v>
       </c>
       <c r="B7" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136703538</v>
       </c>
       <c r="B8" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136703522</v>
       </c>
       <c r="B9" t="n">
-        <v>79239</v>
+        <v>79240</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>136703525</v>
       </c>
       <c r="B10" t="n">
-        <v>79239</v>
+        <v>79240</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>136703533</v>
       </c>
       <c r="B11" t="n">
-        <v>79239</v>
+        <v>79240</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>136703535</v>
       </c>
       <c r="B12" t="n">
-        <v>79239</v>
+        <v>79240</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>136703521</v>
       </c>
       <c r="B13" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>136703523</v>
       </c>
       <c r="B14" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>136703524</v>
       </c>
       <c r="B15" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>136703526</v>
       </c>
       <c r="B16" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         <v>136703528</v>
       </c>
       <c r="B17" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         <v>136703537</v>
       </c>
       <c r="B18" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2519,7 +2519,7 @@
         <v>136703527</v>
       </c>
       <c r="B20" t="n">
-        <v>80072</v>
+        <v>80073</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2621,7 +2621,7 @@
         <v>136703529</v>
       </c>
       <c r="B21" t="n">
-        <v>80072</v>
+        <v>80073</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 11125-2026 artfynd.xlsx
+++ b/artfynd/A 11125-2026 artfynd.xlsx
@@ -887,7 +887,7 @@
         <v>136703536</v>
       </c>
       <c r="B4" t="n">
-        <v>92297</v>
+        <v>92303</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 11125-2026 artfynd.xlsx
+++ b/artfynd/A 11125-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136703532</v>
       </c>
       <c r="B2" t="n">
-        <v>79515</v>
+        <v>79517</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136703530</v>
       </c>
       <c r="B3" t="n">
-        <v>79578</v>
+        <v>79580</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136703536</v>
       </c>
       <c r="B4" t="n">
-        <v>92303</v>
+        <v>92307</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136703519</v>
       </c>
       <c r="B5" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136703531</v>
       </c>
       <c r="B6" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136703534</v>
       </c>
       <c r="B7" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136703538</v>
       </c>
       <c r="B8" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136703522</v>
       </c>
       <c r="B9" t="n">
-        <v>79240</v>
+        <v>79242</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>136703525</v>
       </c>
       <c r="B10" t="n">
-        <v>79240</v>
+        <v>79242</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>136703533</v>
       </c>
       <c r="B11" t="n">
-        <v>79240</v>
+        <v>79242</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>136703535</v>
       </c>
       <c r="B12" t="n">
-        <v>79240</v>
+        <v>79242</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>136703521</v>
       </c>
       <c r="B13" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>136703523</v>
       </c>
       <c r="B14" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>136703524</v>
       </c>
       <c r="B15" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>136703526</v>
       </c>
       <c r="B16" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         <v>136703528</v>
       </c>
       <c r="B17" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         <v>136703537</v>
       </c>
       <c r="B18" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2519,7 +2519,7 @@
         <v>136703527</v>
       </c>
       <c r="B20" t="n">
-        <v>80073</v>
+        <v>80075</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2621,7 +2621,7 @@
         <v>136703529</v>
       </c>
       <c r="B21" t="n">
-        <v>80073</v>
+        <v>80075</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 11125-2026 artfynd.xlsx
+++ b/artfynd/A 11125-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136703532</v>
       </c>
       <c r="B2" t="n">
-        <v>79517</v>
+        <v>79520</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136703530</v>
       </c>
       <c r="B3" t="n">
-        <v>79580</v>
+        <v>79583</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136703536</v>
       </c>
       <c r="B4" t="n">
-        <v>92307</v>
+        <v>92309</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136703519</v>
       </c>
       <c r="B5" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136703531</v>
       </c>
       <c r="B6" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136703534</v>
       </c>
       <c r="B7" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136703538</v>
       </c>
       <c r="B8" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136703522</v>
       </c>
       <c r="B9" t="n">
-        <v>79242</v>
+        <v>79245</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>136703525</v>
       </c>
       <c r="B10" t="n">
-        <v>79242</v>
+        <v>79245</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>136703533</v>
       </c>
       <c r="B11" t="n">
-        <v>79242</v>
+        <v>79245</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>136703535</v>
       </c>
       <c r="B12" t="n">
-        <v>79242</v>
+        <v>79245</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>136703521</v>
       </c>
       <c r="B13" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>136703523</v>
       </c>
       <c r="B14" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>136703524</v>
       </c>
       <c r="B15" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>136703526</v>
       </c>
       <c r="B16" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         <v>136703528</v>
       </c>
       <c r="B17" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         <v>136703537</v>
       </c>
       <c r="B18" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2519,7 +2519,7 @@
         <v>136703527</v>
       </c>
       <c r="B20" t="n">
-        <v>80075</v>
+        <v>80078</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2621,7 +2621,7 @@
         <v>136703529</v>
       </c>
       <c r="B21" t="n">
-        <v>80075</v>
+        <v>80078</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 11125-2026 artfynd.xlsx
+++ b/artfynd/A 11125-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136703532</v>
       </c>
       <c r="B2" t="n">
-        <v>79520</v>
+        <v>79533</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136703530</v>
       </c>
       <c r="B3" t="n">
-        <v>79583</v>
+        <v>79596</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136703536</v>
       </c>
       <c r="B4" t="n">
-        <v>92309</v>
+        <v>92322</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136703519</v>
       </c>
       <c r="B5" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136703531</v>
       </c>
       <c r="B6" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136703534</v>
       </c>
       <c r="B7" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136703538</v>
       </c>
       <c r="B8" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136703522</v>
       </c>
       <c r="B9" t="n">
-        <v>79245</v>
+        <v>79258</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>136703525</v>
       </c>
       <c r="B10" t="n">
-        <v>79245</v>
+        <v>79258</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>136703533</v>
       </c>
       <c r="B11" t="n">
-        <v>79245</v>
+        <v>79258</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>136703535</v>
       </c>
       <c r="B12" t="n">
-        <v>79245</v>
+        <v>79258</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>136703521</v>
       </c>
       <c r="B13" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>136703523</v>
       </c>
       <c r="B14" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>136703524</v>
       </c>
       <c r="B15" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>136703526</v>
       </c>
       <c r="B16" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         <v>136703528</v>
       </c>
       <c r="B17" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         <v>136703537</v>
       </c>
       <c r="B18" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>136703518</v>
       </c>
       <c r="B19" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2519,7 +2519,7 @@
         <v>136703527</v>
       </c>
       <c r="B20" t="n">
-        <v>80078</v>
+        <v>80091</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2621,7 +2621,7 @@
         <v>136703529</v>
       </c>
       <c r="B21" t="n">
-        <v>80078</v>
+        <v>80091</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 11125-2026 artfynd.xlsx
+++ b/artfynd/A 11125-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136703532</v>
       </c>
       <c r="B2" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136703530</v>
       </c>
       <c r="B3" t="n">
-        <v>79596</v>
+        <v>79598</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136703536</v>
       </c>
       <c r="B4" t="n">
-        <v>92322</v>
+        <v>92324</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136703519</v>
       </c>
       <c r="B5" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136703531</v>
       </c>
       <c r="B6" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136703534</v>
       </c>
       <c r="B7" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136703538</v>
       </c>
       <c r="B8" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136703522</v>
       </c>
       <c r="B9" t="n">
-        <v>79258</v>
+        <v>79260</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>136703525</v>
       </c>
       <c r="B10" t="n">
-        <v>79258</v>
+        <v>79260</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>136703533</v>
       </c>
       <c r="B11" t="n">
-        <v>79258</v>
+        <v>79260</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>136703535</v>
       </c>
       <c r="B12" t="n">
-        <v>79258</v>
+        <v>79260</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>136703521</v>
       </c>
       <c r="B13" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>136703523</v>
       </c>
       <c r="B14" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>136703524</v>
       </c>
       <c r="B15" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>136703526</v>
       </c>
       <c r="B16" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         <v>136703528</v>
       </c>
       <c r="B17" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         <v>136703537</v>
       </c>
       <c r="B18" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>136703518</v>
       </c>
       <c r="B19" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2519,7 +2519,7 @@
         <v>136703527</v>
       </c>
       <c r="B20" t="n">
-        <v>80091</v>
+        <v>80093</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2621,7 +2621,7 @@
         <v>136703529</v>
       </c>
       <c r="B21" t="n">
-        <v>80091</v>
+        <v>80093</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 11125-2026 artfynd.xlsx
+++ b/artfynd/A 11125-2026 artfynd.xlsx
@@ -887,7 +887,7 @@
         <v>136703536</v>
       </c>
       <c r="B4" t="n">
-        <v>92324</v>
+        <v>92327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 11125-2026 artfynd.xlsx
+++ b/artfynd/A 11125-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136703532</v>
       </c>
       <c r="B2" t="n">
-        <v>79535</v>
+        <v>79545</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136703530</v>
       </c>
       <c r="B3" t="n">
-        <v>79598</v>
+        <v>79608</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136703536</v>
       </c>
       <c r="B4" t="n">
-        <v>92327</v>
+        <v>92337</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136703519</v>
       </c>
       <c r="B5" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136703531</v>
       </c>
       <c r="B6" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136703534</v>
       </c>
       <c r="B7" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136703538</v>
       </c>
       <c r="B8" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136703522</v>
       </c>
       <c r="B9" t="n">
-        <v>79260</v>
+        <v>79270</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>136703525</v>
       </c>
       <c r="B10" t="n">
-        <v>79260</v>
+        <v>79270</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>136703533</v>
       </c>
       <c r="B11" t="n">
-        <v>79260</v>
+        <v>79270</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>136703535</v>
       </c>
       <c r="B12" t="n">
-        <v>79260</v>
+        <v>79270</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>136703521</v>
       </c>
       <c r="B13" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>136703523</v>
       </c>
       <c r="B14" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>136703524</v>
       </c>
       <c r="B15" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>136703526</v>
       </c>
       <c r="B16" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         <v>136703528</v>
       </c>
       <c r="B17" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         <v>136703537</v>
       </c>
       <c r="B18" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>136703518</v>
       </c>
       <c r="B19" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2519,7 +2519,7 @@
         <v>136703527</v>
       </c>
       <c r="B20" t="n">
-        <v>80093</v>
+        <v>80103</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2621,7 +2621,7 @@
         <v>136703529</v>
       </c>
       <c r="B21" t="n">
-        <v>80093</v>
+        <v>80103</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
